--- a/WaterDPP/language/language.xlsx
+++ b/WaterDPP/language/language.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C184"/>
+  <dimension ref="A1:C233"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,10 +415,10 @@
         <v>app_title</v>
       </c>
       <c r="B2" t="str">
-        <v>循環玻璃瓶裝水數位產品護照管理系統 V_dp_15</v>
+        <v>循環玻璃瓶裝水數位產品護照管理系統 V_dp_16</v>
       </c>
       <c r="C2" t="str">
-        <v>Circular Glass Bottled Water DPP Management System V_dp_15</v>
+        <v>Circular Glass Bottled Water DPP Management System V_dp_16</v>
       </c>
     </row>
     <row r="3">
@@ -426,10 +426,10 @@
         <v>version_info</v>
       </c>
       <c r="B3" t="str">
-        <v>修訂版本時間：20260908</v>
+        <v>修訂版本時間：20260909</v>
       </c>
       <c r="C3" t="str">
-        <v>Version Date: 20260908</v>
+        <v>Version Date: 20260909</v>
       </c>
     </row>
     <row r="4">
@@ -569,10 +569,10 @@
         <v>page1_title</v>
       </c>
       <c r="B16" t="str">
-        <v>頁面一：系統總覽 (Dashboard V_dp_15)</v>
+        <v>頁面一：系統總覽 (Dashboard V_dp_16)</v>
       </c>
       <c r="C16" t="str">
-        <v>Page 1: Dashboard V_dp_15</v>
+        <v>Page 1: Dashboard V_dp_16</v>
       </c>
     </row>
     <row r="17">
@@ -602,10 +602,10 @@
         <v>page4_title</v>
       </c>
       <c r="B19" t="str">
-        <v>頁面四：產品追溯管理 (V_dp_15)</v>
+        <v>頁面四：產品追溯管理 (V_dp_16)</v>
       </c>
       <c r="C19" t="str">
-        <v>Page 4: Traceability Management (V_dp_15)</v>
+        <v>Page 4: Traceability Management (V_dp_16)</v>
       </c>
     </row>
     <row r="20">
@@ -624,10 +624,10 @@
         <v>page6_title</v>
       </c>
       <c r="B21" t="str">
-        <v>頁面六：消費者護照查詢 (V_dp_15)</v>
+        <v>頁面六：消費者護照查詢 (V_dp_16)</v>
       </c>
       <c r="C21" t="str">
-        <v>Page 6: Consumer Passport (V_dp_15)</v>
+        <v>Page 6: Consumer Passport (V_dp_16)</v>
       </c>
     </row>
     <row r="22">
@@ -2193,260 +2193,799 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>label_product_name</v>
+        <v>label_grai</v>
       </c>
       <c r="B162" t="str">
-        <v>產品名稱：</v>
+        <v>GRAI 代碼：</v>
       </c>
       <c r="C162" t="str">
-        <v>Product Name:</v>
+        <v>GRAI Code:</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>label_grai</v>
+        <v>label_status</v>
       </c>
       <c r="B163" t="str">
-        <v>GRAI 代碼：</v>
+        <v>瓶子當前狀態：</v>
       </c>
       <c r="C163" t="str">
-        <v>GRAI Code:</v>
+        <v>Current Bottle Status:</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>label_status</v>
+        <v>label_avail_status</v>
       </c>
       <c r="B164" t="str">
-        <v>瓶子當前狀態：</v>
+        <v>可用物料狀態：</v>
       </c>
       <c r="C164" t="str">
-        <v>Current Bottle Status:</v>
+        <v>Availability:</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>label_avail_status</v>
+        <v>label_location</v>
       </c>
       <c r="B165" t="str">
-        <v>可用物料狀態：</v>
+        <v>所在實體區域：</v>
       </c>
       <c r="C165" t="str">
-        <v>Availability:</v>
+        <v>Physical Location:</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>label_location</v>
+        <v>label_cycle_count</v>
       </c>
       <c r="B166" t="str">
-        <v>所在實體區域：</v>
+        <v>循環次數：</v>
       </c>
       <c r="C166" t="str">
-        <v>Physical Location:</v>
+        <v>Cycle Count:</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>label_cycle_count</v>
+        <v>label_update_time</v>
       </c>
       <c r="B167" t="str">
-        <v>循環次數：</v>
+        <v>最新狀態改變時間：</v>
       </c>
       <c r="C167" t="str">
-        <v>Cycle Count:</v>
+        <v>Last Status Change:</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>label_update_time</v>
+        <v>label_history_batch</v>
       </c>
       <c r="B168" t="str">
-        <v>最新狀態改變時間：</v>
+        <v>歷史批次紀錄：</v>
       </c>
       <c r="C168" t="str">
-        <v>Last Status Change:</v>
+        <v>Historical Batch Records:</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>label_history_batch</v>
+        <v>label_remark</v>
       </c>
       <c r="B169" t="str">
-        <v>歷史批次紀錄：</v>
+        <v>備註標記：</v>
       </c>
       <c r="C169" t="str">
-        <v>Historical Batch Records:</v>
+        <v>Remarks:</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>label_remark</v>
+        <v>esg_title</v>
       </c>
       <c r="B170" t="str">
-        <v>備註標記：</v>
+        <v>🌱 ESG 產品碳足跡履歷</v>
       </c>
       <c r="C170" t="str">
-        <v>Remarks:</v>
+        <v>🌱 ESG Carbon Footprint History</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>esg_title</v>
+        <v>label_esg_total</v>
       </c>
       <c r="B171" t="str">
-        <v>🌱 ESG 產品碳足跡履歷</v>
+        <v>全生命週期總碳排放：</v>
       </c>
       <c r="C171" t="str">
-        <v>🌱 ESG Carbon Footprint History</v>
+        <v>Total Lifecycle Carbon Emission:</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>label_esg_total</v>
+        <v>esg_raw</v>
       </c>
       <c r="B172" t="str">
-        <v>全生命週期總碳排放：</v>
+        <v>原料與製造</v>
       </c>
       <c r="C172" t="str">
-        <v>Total Lifecycle Carbon Emission:</v>
+        <v>Raw Material &amp; Manufacturing</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>esg_raw</v>
+        <v>esg_fill</v>
       </c>
       <c r="B173" t="str">
-        <v>原料與製造</v>
+        <v>灌裝生產</v>
       </c>
       <c r="C173" t="str">
-        <v>Raw Material &amp; Manufacturing</v>
+        <v>Filling Production</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>esg_fill</v>
+        <v>esg_log</v>
       </c>
       <c r="B174" t="str">
-        <v>灌裝生產</v>
+        <v>物流運輸</v>
       </c>
       <c r="C174" t="str">
-        <v>Filling Production</v>
+        <v>Logistics &amp; Transportation</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>esg_log</v>
+        <v>esg_rec</v>
       </c>
       <c r="B175" t="str">
-        <v>物流運輸</v>
+        <v>回收與清洗</v>
       </c>
       <c r="C175" t="str">
-        <v>Logistics &amp; Transportation</v>
+        <v>Recycling &amp; Cleaning</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>esg_rec</v>
+        <v>available_stock_title</v>
       </c>
       <c r="B176" t="str">
-        <v>回收與清洗</v>
+        <v>當前可用物料庫存統計</v>
       </c>
       <c r="C176" t="str">
-        <v>Recycling &amp; Cleaning</v>
+        <v>Current Available Inventory Statistics</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>available_stock_title</v>
+        <v>qa_return_stock</v>
       </c>
       <c r="B177" t="str">
-        <v>當前可用物料庫存統計</v>
+        <v>可灌裝回收物料區 (QA回收入庫)</v>
       </c>
       <c r="C177" t="str">
-        <v>Current Available Inventory Statistics</v>
+        <v>Refillable Recycled Material (QA Return)</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>qa_return_stock</v>
+        <v>new_stock</v>
       </c>
       <c r="B178" t="str">
-        <v>可灌裝回收物料區 (QA回收入庫)</v>
+        <v>新物料庫存區 (新庫存)</v>
       </c>
       <c r="C178" t="str">
-        <v>Refillable Recycled Material (QA Return)</v>
+        <v>New Material Inventory (New)</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>new_stock</v>
+        <v>reserved_stock</v>
       </c>
       <c r="B179" t="str">
-        <v>新物料庫存區 (新庫存)</v>
+        <v>已預訂物料</v>
       </c>
       <c r="C179" t="str">
-        <v>New Material Inventory (New)</v>
+        <v>Reserved Material</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>reserved_stock</v>
+        <v>total_available</v>
       </c>
       <c r="B180" t="str">
-        <v>已預訂物料</v>
+        <v>總計可用庫存</v>
       </c>
       <c r="C180" t="str">
-        <v>Reserved Material</v>
+        <v>Total Available Inventory</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>total_available</v>
+        <v>sn_not_generated</v>
       </c>
       <c r="B181" t="str">
-        <v>總計可用庫存</v>
+        <v>尚未排產生成</v>
       </c>
       <c r="C181" t="str">
-        <v>Total Available Inventory</v>
+        <v>Not generated yet</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>sn_not_generated</v>
+        <v>label_avail_yes</v>
       </c>
       <c r="B182" t="str">
-        <v>尚未排產生成</v>
+        <v>✔ 可用物料</v>
       </c>
       <c r="C182" t="str">
-        <v>Not generated yet</v>
+        <v>✔ Available</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>label_avail_yes</v>
+        <v>label_avail_no</v>
       </c>
       <c r="B183" t="str">
-        <v>✔ 可用物料</v>
+        <v>✘ 不可用物料</v>
       </c>
       <c r="C183" t="str">
-        <v>✔ Available</v>
+        <v>✘ Unavailable</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>label_avail_no</v>
+        <v>unknown_product</v>
       </c>
       <c r="B184" t="str">
-        <v>✘ 不可用物料</v>
+        <v>未知產品</v>
       </c>
       <c r="C184" t="str">
-        <v>✘ Unavailable</v>
+        <v>Unknown Product</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>no_special_remark</v>
+      </c>
+      <c r="B185" t="str">
+        <v>無特殊標註</v>
+      </c>
+      <c r="C185" t="str">
+        <v>No special remark</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>qa_report_download</v>
+      </c>
+      <c r="B186" t="str">
+        <v>QA報告下載</v>
+      </c>
+      <c r="C186" t="str">
+        <v>QA Report Download</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>no_qa_report</v>
+      </c>
+      <c r="B187" t="str">
+        <v>非可銷售, 無關聯的QA報告</v>
+      </c>
+      <c r="C187" t="str">
+        <v>Not sellable, no associated QA report</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>report_not_uploaded</v>
+      </c>
+      <c r="B188" t="str">
+        <v>報告尚未上傳</v>
+      </c>
+      <c r="C188" t="str">
+        <v>Report not uploaded</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>no_qa_report_or_not_uploaded</v>
+      </c>
+      <c r="B189" t="str">
+        <v>無關聯的QA報告或報告未上傳</v>
+      </c>
+      <c r="C189" t="str">
+        <v>No associated QA report or report not uploaded</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>search_by_batch</v>
+      </c>
+      <c r="B190" t="str">
+        <v>批次號</v>
+      </c>
+      <c r="C190" t="str">
+        <v>Batch No.</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>search_placeholder</v>
+      </c>
+      <c r="B191" t="str">
+        <v>搜尋序列號或 GRAI</v>
+      </c>
+      <c r="C191" t="str">
+        <v>Search Serial No. or GRAI</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>search_type_serial</v>
+      </c>
+      <c r="B192" t="str">
+        <v>序列號或GRAI</v>
+      </c>
+      <c r="C192" t="str">
+        <v>Serial No. or GRAI</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>search_type_batch</v>
+      </c>
+      <c r="B193" t="str">
+        <v>批次</v>
+      </c>
+      <c r="C193" t="str">
+        <v>Batch</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>sort_batch_no</v>
+      </c>
+      <c r="B194" t="str">
+        <v>最新批次號 ⇅</v>
+      </c>
+      <c r="C194" t="str">
+        <v>Latest Batch No. ⇅</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>btn_upload_qa_report</v>
+      </c>
+      <c r="B195" t="str">
+        <v>📤 QA報告上傳</v>
+      </c>
+      <c r="C195" t="str">
+        <v>📤 Upload QA Report</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>upload_simulation_msg</v>
+      </c>
+      <c r="B196" t="str">
+        <v>因為模擬演示, 這裡模擬QA報告上傳功能, 實際報告將由管理員手動放置到伺服器中</v>
+      </c>
+      <c r="C196" t="str">
+        <v>For simulation, this simulates QA report upload; actual report will be manually placed by administrator.</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>scan_time</v>
+      </c>
+      <c r="B197" t="str">
+        <v>掃碼時間</v>
+      </c>
+      <c r="C197" t="str">
+        <v>Scan Time</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>production_date</v>
+      </c>
+      <c r="B198" t="str">
+        <v>生產日期</v>
+      </c>
+      <c r="C198" t="str">
+        <v>Production Date</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>expiry_date</v>
+      </c>
+      <c r="B199" t="str">
+        <v>產品效期</v>
+      </c>
+      <c r="C199" t="str">
+        <v>Expiry Date</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>qa_report</v>
+      </c>
+      <c r="B200" t="str">
+        <v>QA報告</v>
+      </c>
+      <c r="C200" t="str">
+        <v>QA Report</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>non_sale_no_prod_date</v>
+      </c>
+      <c r="B201" t="str">
+        <v>非銷售狀態, 無生產日期</v>
+      </c>
+      <c r="C201" t="str">
+        <v>Non-sale status, no production date</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>no_prod_date_no_expiry</v>
+      </c>
+      <c r="B202" t="str">
+        <v>無生產日期, 無產品效期</v>
+      </c>
+      <c r="C202" t="str">
+        <v>No production date, no expiry date</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>non_sale_no_qa_report</v>
+      </c>
+      <c r="B203" t="str">
+        <v>非銷售狀態, 無QA報告</v>
+      </c>
+      <c r="C203" t="str">
+        <v>Non-sale status, no QA report</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>download</v>
+      </c>
+      <c r="B204" t="str">
+        <v>下載</v>
+      </c>
+      <c r="C204" t="str">
+        <v>Download</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>confirm</v>
+      </c>
+      <c r="B205" t="str">
+        <v>確認</v>
+      </c>
+      <c r="C205" t="str">
+        <v>Confirm</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>option_all_status</v>
+      </c>
+      <c r="B206" t="str">
+        <v>全部狀態 (全選)</v>
+      </c>
+      <c r="C206" t="str">
+        <v>All Statuses (Select All)</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>option_all_area</v>
+      </c>
+      <c r="B207" t="str">
+        <v>全部區域 (全選)</v>
+      </c>
+      <c r="C207" t="str">
+        <v>All Areas (Select All)</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>option_all_order_status</v>
+      </c>
+      <c r="B208" t="str">
+        <v>全部訂單狀態</v>
+      </c>
+      <c r="C208" t="str">
+        <v>All Order Statuses</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>batch_draft</v>
+      </c>
+      <c r="B209" t="str">
+        <v>草稿</v>
+      </c>
+      <c r="C209" t="str">
+        <v>Draft</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>batch_new</v>
+      </c>
+      <c r="B210" t="str">
+        <v>新建立</v>
+      </c>
+      <c r="C210" t="str">
+        <v>New</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>batch_pushed</v>
+      </c>
+      <c r="B211" t="str">
+        <v>已推送至生產線</v>
+      </c>
+      <c r="C211" t="str">
+        <v>Pushed to Production</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>batch_completed</v>
+      </c>
+      <c r="B212" t="str">
+        <v>已完成生產</v>
+      </c>
+      <c r="C212" t="str">
+        <v>Production Completed</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>batch_abnormal</v>
+      </c>
+      <c r="B213" t="str">
+        <v>異常</v>
+      </c>
+      <c r="C213" t="str">
+        <v>Abnormal</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>placeholder_search</v>
+      </c>
+      <c r="B214" t="str">
+        <v>搜尋序列號 (如 A00001) 或 GRAI...</v>
+      </c>
+      <c r="C214" t="str">
+        <v>Search Serial No. (e.g., A00001) or GRAI...</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>placeholder_batch_search</v>
+      </c>
+      <c r="B215" t="str">
+        <v>搜尋訂單號 (如 ORD-...) 或 客戶名稱...</v>
+      </c>
+      <c r="C215" t="str">
+        <v>Search Order No. (e.g., ORD-...) or Client Name...</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>placeholder_serial</v>
+      </c>
+      <c r="B216" t="str">
+        <v>輸入序列號</v>
+      </c>
+      <c r="C216" t="str">
+        <v>Enter Serial No.</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>placeholder_remark</v>
+      </c>
+      <c r="B217" t="str">
+        <v>請輸入備註...</v>
+      </c>
+      <c r="C217" t="str">
+        <v>Enter remarks...</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>placeholder_batch_remark</v>
+      </c>
+      <c r="B218" t="str">
+        <v>請輸入批次更新備註...</v>
+      </c>
+      <c r="C218" t="str">
+        <v>Enter batch update remarks...</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>pagination_info</v>
+      </c>
+      <c r="B219" t="str">
+        <v>顯示 {0} - {1} 筆，共 {2} 筆資料</v>
+      </c>
+      <c r="C219" t="str">
+        <v>Showing {0} - {1} of {2} records</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>selected_count</v>
+      </c>
+      <c r="B220" t="str">
+        <v>已勾選 {0} 筆</v>
+      </c>
+      <c r="C220" t="str">
+        <v>Selected: {0}</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>modal_add_title</v>
+      </c>
+      <c r="B221" t="str">
+        <v>新增資料</v>
+      </c>
+      <c r="C221" t="str">
+        <v>Add Data</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>status_modal_title</v>
+      </c>
+      <c r="B222" t="str">
+        <v>變更瓶子生命週期狀態</v>
+      </c>
+      <c r="C222" t="str">
+        <v>Change Bottle Lifecycle Status</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>batch_status_modal_title</v>
+      </c>
+      <c r="B223" t="str">
+        <v>☑️ 批次修改已勾選項目狀態</v>
+      </c>
+      <c r="C223" t="str">
+        <v>☑️ Batch Modify Selected Items Status</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>selected_count_modal</v>
+      </c>
+      <c r="B224" t="str">
+        <v>目前已勾選筆數：</v>
+      </c>
+      <c r="C224" t="str">
+        <v>Currently Selected:</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>esg_modal_title</v>
+      </c>
+      <c r="B225" t="str">
+        <v>🌱 ESG 碳排放環節數據設定</v>
+      </c>
+      <c r="C225" t="str">
+        <v>🌱 ESG Carbon Emission Settings</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>esg_modal_desc</v>
+      </c>
+      <c r="B226" t="str">
+        <v>請輸入產品各生命週期環節之碳排放值（單位：kgCO₂e / 瓶），系統將自動進行加總計算，並連動至 DPP 護照。</v>
+      </c>
+      <c r="C226" t="str">
+        <v>Please enter the carbon emission values for each lifecycle stage (unit: kgCO₂e / bottle). The system will automatically calculate the total and link to the DPP.</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>esg_raw_label</v>
+      </c>
+      <c r="B227" t="str">
+        <v>1. 原料與容器製造碳排放：</v>
+      </c>
+      <c r="C227" t="str">
+        <v>1. Raw Material &amp; Container Manufacturing:</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>esg_fill_label</v>
+      </c>
+      <c r="B228" t="str">
+        <v>2. 灌裝生產與包裝碳排放：</v>
+      </c>
+      <c r="C228" t="str">
+        <v>2. Filling &amp; Packaging:</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>esg_log_label</v>
+      </c>
+      <c r="B229" t="str">
+        <v>3. 物流運輸與通路配送碳排放：</v>
+      </c>
+      <c r="C229" t="str">
+        <v>3. Logistics &amp; Distribution:</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>esg_rec_label</v>
+      </c>
+      <c r="B230" t="str">
+        <v>4. 回收清洗與循環處置碳排放：</v>
+      </c>
+      <c r="C230" t="str">
+        <v>4. Recycling &amp; Cleaning:</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>esg_total_label</v>
+      </c>
+      <c r="B231" t="str">
+        <v>全生命週期碳足跡總和 (Total Carbon Footprint)：</v>
+      </c>
+      <c r="C231" t="str">
+        <v>Total Carbon Footprint:</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>qr_modal_title</v>
+      </c>
+      <c r="B232" t="str">
+        <v>GS1 Digital Link 二維碼</v>
+      </c>
+      <c r="C232" t="str">
+        <v>GS1 Digital Link QR Code</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>btn_query_passport</v>
+      </c>
+      <c r="B233" t="str">
+        <v>📱 查詢護照履歷</v>
+      </c>
+      <c r="C233" t="str">
+        <v>📱 Query Passport</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C184"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C233"/>
   </ignoredErrors>
 </worksheet>
 </file>